--- a/base_datas/percentis_limites.xlsx
+++ b/base_datas/percentis_limites.xlsx
@@ -371,7 +371,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3720.640855449029</v>
+        <v>3783.517528201794</v>
       </c>
     </row>
     <row r="3">
@@ -379,7 +379,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4020.43254352445</v>
+        <v>4043.830118141701</v>
       </c>
     </row>
     <row r="4">
@@ -387,7 +387,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4260.965191842971</v>
+        <v>4276.506480522412</v>
       </c>
     </row>
     <row r="5">
@@ -395,7 +395,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4386.222895885941</v>
+        <v>4398.943671060034</v>
       </c>
     </row>
     <row r="6">
@@ -403,7 +403,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4529.074472815171</v>
+        <v>4537.542160265371</v>
       </c>
     </row>
     <row r="7">
@@ -411,7 +411,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>4621.086516457318</v>
+        <v>4628.425084736697</v>
       </c>
     </row>
     <row r="8">
@@ -419,7 +419,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>4703.825574258188</v>
+        <v>4710.670353425682</v>
       </c>
     </row>
     <row r="9">
@@ -427,7 +427,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>4788.844840400487</v>
+        <v>4793.209970764273</v>
       </c>
     </row>
     <row r="10">
@@ -435,7 +435,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4856.810497789301</v>
+        <v>4864.080450446882</v>
       </c>
     </row>
     <row r="11">
@@ -443,7 +443,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4917.328461698527</v>
+        <v>4920.894694196867</v>
       </c>
     </row>
     <row r="12">
@@ -451,7 +451,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>4989.311973043983</v>
+        <v>4997.999947784402</v>
       </c>
     </row>
     <row r="13">
@@ -459,7 +459,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>5041.966034256943</v>
+        <v>5047.313032511748</v>
       </c>
     </row>
     <row r="14">
@@ -467,7 +467,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>5090.696688515834</v>
+        <v>5097.646334644306</v>
       </c>
     </row>
     <row r="15">
@@ -475,7 +475,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>5146.882635360159</v>
+        <v>5151.936085629291</v>
       </c>
     </row>
     <row r="16">
@@ -483,7 +483,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>5193.313548276376</v>
+        <v>5195.257367918696</v>
       </c>
     </row>
     <row r="17">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>5240.72613063585</v>
+        <v>5243.888182582758</v>
       </c>
     </row>
     <row r="18">
@@ -499,7 +499,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>5293.180218257061</v>
+        <v>5298.43482380017</v>
       </c>
     </row>
     <row r="19">
@@ -507,7 +507,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5351.300378781207</v>
+        <v>5356.002514867426</v>
       </c>
     </row>
     <row r="20">
@@ -515,7 +515,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>5395.753174453925</v>
+        <v>5399.958804818683</v>
       </c>
     </row>
     <row r="21">
@@ -523,7 +523,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>5454.866657571823</v>
+        <v>5459.69036118429</v>
       </c>
     </row>
     <row r="22">
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>5497.481792534185</v>
+        <v>5501.854652749463</v>
       </c>
     </row>
     <row r="23">
@@ -539,7 +539,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>5557.844238612485</v>
+        <v>5560.35896272558</v>
       </c>
     </row>
     <row r="24">
@@ -547,7 +547,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>5600.755589613411</v>
+        <v>5604.610066121589</v>
       </c>
     </row>
     <row r="25">
@@ -555,7 +555,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5647.12994817261</v>
+        <v>5650.14534198159</v>
       </c>
     </row>
     <row r="26">
@@ -563,7 +563,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>5693.660204986585</v>
+        <v>5694.896187233752</v>
       </c>
     </row>
     <row r="27">
@@ -571,7 +571,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>5747.149766662462</v>
+        <v>5750.459341497017</v>
       </c>
     </row>
     <row r="28">
@@ -579,7 +579,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>5799.439321641961</v>
+        <v>5804.481633985016</v>
       </c>
     </row>
     <row r="29">
@@ -587,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>5854.134427037035</v>
+        <v>5859.29326201102</v>
       </c>
     </row>
     <row r="30">
@@ -595,7 +595,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>5895.523275354977</v>
+        <v>5897.487123340857</v>
       </c>
     </row>
     <row r="31">
@@ -603,7 +603,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>5942.260885042602</v>
+        <v>5947.618373823729</v>
       </c>
     </row>
     <row r="32">
@@ -611,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>5991.482531212046</v>
+        <v>5994.657968195213</v>
       </c>
     </row>
     <row r="33">
@@ -619,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>6040.37035775852</v>
+        <v>6041.546995822168</v>
       </c>
     </row>
     <row r="34">
@@ -627,7 +627,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>6100.702537821503</v>
+        <v>6102.732844825643</v>
       </c>
     </row>
     <row r="35">
@@ -635,7 +635,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>6141.002918606204</v>
+        <v>6143.083729359993</v>
       </c>
     </row>
     <row r="36">
@@ -643,7 +643,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>6179.630539365918</v>
+        <v>6181.991234364455</v>
       </c>
     </row>
     <row r="37">
@@ -651,7 +651,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>6236.835597967122</v>
+        <v>6241.11865647752</v>
       </c>
     </row>
     <row r="38">
@@ -659,7 +659,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>6294.013451710318</v>
+        <v>6295.714969536785</v>
       </c>
     </row>
     <row r="39">
@@ -667,7 +667,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>6346.900404696386</v>
+        <v>6350.935549590362</v>
       </c>
     </row>
     <row r="40">
@@ -675,7 +675,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>6407.833634053301</v>
+        <v>6412.001263718164</v>
       </c>
     </row>
     <row r="41">
@@ -683,7 +683,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>6449.914482894344</v>
+        <v>6451.916683814181</v>
       </c>
     </row>
     <row r="42">
@@ -691,7 +691,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>6501.117095080152</v>
+        <v>6504.031571731387</v>
       </c>
     </row>
     <row r="43">
@@ -699,7 +699,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>6547.543493537919</v>
+        <v>6549.009022784168</v>
       </c>
     </row>
     <row r="44">
@@ -707,7 +707,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>6590.705321814321</v>
+        <v>6593.435311583595</v>
       </c>
     </row>
     <row r="45">
@@ -715,7 +715,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>6644.867494833448</v>
+        <v>6647.719715803658</v>
       </c>
     </row>
     <row r="46">
@@ -723,7 +723,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>6707.015412421932</v>
+        <v>6710.269496607392</v>
       </c>
     </row>
     <row r="47">
@@ -731,7 +731,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>6753.597977039327</v>
+        <v>6753.918725096402</v>
       </c>
     </row>
     <row r="48">
@@ -739,7 +739,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>6810.95773356797</v>
+        <v>6811.851391339047</v>
       </c>
     </row>
     <row r="49">
@@ -747,7 +747,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>6864.765639223935</v>
+        <v>6872.040003895903</v>
       </c>
     </row>
     <row r="50">
@@ -755,7 +755,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>6916.818908228905</v>
+        <v>6921.182290360393</v>
       </c>
     </row>
     <row r="51">
@@ -763,7 +763,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>6983.108357808529</v>
+        <v>6986.327522142778</v>
       </c>
     </row>
     <row r="52">
@@ -771,7 +771,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>7047.184759110729</v>
+        <v>7051.553797177016</v>
       </c>
     </row>
     <row r="53">
@@ -779,7 +779,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>7109.778556673895</v>
+        <v>7111.62153289072</v>
       </c>
     </row>
     <row r="54">
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>7169.458299201263</v>
+        <v>7170.359479660136</v>
       </c>
     </row>
     <row r="55">
@@ -795,7 +795,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>7241.252320919804</v>
+        <v>7245.354316532658</v>
       </c>
     </row>
     <row r="56">
@@ -803,7 +803,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>7300.87061873361</v>
+        <v>7302.223806863502</v>
       </c>
     </row>
     <row r="57">
@@ -811,7 +811,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>7370.434208837208</v>
+        <v>7372.02891221321</v>
       </c>
     </row>
     <row r="58">
@@ -819,7 +819,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>7442.736558313551</v>
+        <v>7447.678110022447</v>
       </c>
     </row>
     <row r="59">
@@ -827,7 +827,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>7518.23424152701</v>
+        <v>7520.957470192421</v>
       </c>
     </row>
     <row r="60">
@@ -835,7 +835,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>7584.369601495258</v>
+        <v>7585.015540387088</v>
       </c>
     </row>
     <row r="61">
@@ -843,7 +843,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>7662.945606070226</v>
+        <v>7664.205969414892</v>
       </c>
     </row>
     <row r="62">
@@ -851,7 +851,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>7731.114522622578</v>
+        <v>7732.124232317489</v>
       </c>
     </row>
     <row r="63">
@@ -859,7 +859,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>7794.366674613875</v>
+        <v>7800.519804032767</v>
       </c>
     </row>
     <row r="64">
@@ -867,7 +867,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>7881.367874550932</v>
+        <v>7882.938559587422</v>
       </c>
     </row>
     <row r="65">
@@ -875,7 +875,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>7961.966307053915</v>
+        <v>7963.411449567946</v>
       </c>
     </row>
     <row r="66">
@@ -883,7 +883,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>8047.80003817274</v>
+        <v>8048.316206696706</v>
       </c>
     </row>
     <row r="67">
@@ -891,7 +891,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>8133.51891268191</v>
+        <v>8137.42321733596</v>
       </c>
     </row>
     <row r="68">
@@ -899,7 +899,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>8232.429002668181</v>
+        <v>8234.481493439154</v>
       </c>
     </row>
     <row r="69">
@@ -907,7 +907,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>8352.19816268505</v>
+        <v>8352.690632914004</v>
       </c>
     </row>
     <row r="70">
@@ -915,7 +915,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>8458.922765049045</v>
+        <v>8462.291450176366</v>
       </c>
     </row>
     <row r="71">
@@ -923,7 +923,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>8581.320636001732</v>
+        <v>8581.780787469146</v>
       </c>
     </row>
     <row r="72">
@@ -931,7 +931,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>8674.423037500204</v>
+        <v>8677.685070825606</v>
       </c>
     </row>
     <row r="73">
@@ -939,7 +939,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>8796.898219246381</v>
+        <v>8798.670405191613</v>
       </c>
     </row>
     <row r="74">
@@ -947,7 +947,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>8925.987985792985</v>
+        <v>8926.592841410431</v>
       </c>
     </row>
     <row r="75">
@@ -955,7 +955,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>9051.408431266713</v>
+        <v>9053.562453878774</v>
       </c>
     </row>
     <row r="76">
@@ -963,7 +963,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>9149.666512766635</v>
+        <v>9151.116817854683</v>
       </c>
     </row>
     <row r="77">
@@ -971,7 +971,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>9331.547540265405</v>
+        <v>9336.877661607168</v>
       </c>
     </row>
     <row r="78">
@@ -979,7 +979,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>9482.775242345153</v>
+        <v>9485.189269367514</v>
       </c>
     </row>
     <row r="79">
@@ -987,7 +987,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>9670.615790472251</v>
+        <v>9672.249035515269</v>
       </c>
     </row>
     <row r="80">
@@ -995,7 +995,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>9858.094911319706</v>
+        <v>9858.57679569535</v>
       </c>
     </row>
     <row r="81">
@@ -1003,7 +1003,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>10012.30264577889</v>
+        <v>10012.81267432013</v>
       </c>
     </row>
     <row r="82">
@@ -1011,7 +1011,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>10231.05090545293</v>
+        <v>10232.40804954534</v>
       </c>
     </row>
     <row r="83">
@@ -1019,7 +1019,7 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>10427.63045182627</v>
+        <v>10429.92270414943</v>
       </c>
     </row>
     <row r="84">
@@ -1027,7 +1027,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>10638.77571069414</v>
+        <v>10639.83053125348</v>
       </c>
     </row>
     <row r="85">
@@ -1035,7 +1035,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>10852.24582973458</v>
+        <v>10852.58001560144</v>
       </c>
     </row>
     <row r="86">
@@ -1043,7 +1043,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>11178.62587568799</v>
+        <v>11179.33208177038</v>
       </c>
     </row>
     <row r="87">
@@ -1051,7 +1051,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>11445.24371367402</v>
+        <v>11445.19109261103</v>
       </c>
     </row>
     <row r="88">
@@ -1059,7 +1059,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>11768.59855747335</v>
+        <v>11768.32692532717</v>
       </c>
     </row>
     <row r="89">
@@ -1067,7 +1067,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>12044.2930925831</v>
+        <v>12044.20110407062</v>
       </c>
     </row>
     <row r="90">
@@ -1075,7 +1075,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>12352.09416846354</v>
+        <v>12351.81909052615</v>
       </c>
     </row>
     <row r="91">
@@ -1083,7 +1083,7 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>12662.88546246381</v>
+        <v>12662.64575159755</v>
       </c>
     </row>
     <row r="92">
@@ -1091,7 +1091,7 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>12902.74819640071</v>
+        <v>12901.0005898265</v>
       </c>
     </row>
     <row r="93">
@@ -1099,7 +1099,7 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>13327.26740359681</v>
+        <v>13326.04151809475</v>
       </c>
     </row>
     <row r="94">
@@ -1107,7 +1107,7 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>13870.00491009472</v>
+        <v>13868.31959080755</v>
       </c>
     </row>
     <row r="95">
@@ -1115,7 +1115,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>14465.25176513633</v>
+        <v>14454.743427219</v>
       </c>
     </row>
     <row r="96">
@@ -1123,7 +1123,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>14979.23831412986</v>
+        <v>14975.08589897178</v>
       </c>
     </row>
     <row r="97">
@@ -1131,7 +1131,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>15796.86720727127</v>
+        <v>15795.55661123647</v>
       </c>
     </row>
     <row r="98">
@@ -1139,7 +1139,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>16782.51601940247</v>
+        <v>16760.57532372178</v>
       </c>
     </row>
     <row r="99">
@@ -1147,7 +1147,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>18173.89164957556</v>
+        <v>18164.52941894309</v>
       </c>
     </row>
     <row r="100">
@@ -1155,7 +1155,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>20359.88560192149</v>
+        <v>20335.46910891176</v>
       </c>
     </row>
   </sheetData>
